--- a/virtual-physics-lab/app/dl/NJC_Q3h_table.xlsx
+++ b/virtual-physics-lab/app/dl/NJC_Q3h_table.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +102,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -191,7 +195,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>T² against cos θ</a:t>
+              <a:t>T² against cos φ</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -258,7 +262,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>cos θ</a:t>
+                  <a:t>cos φ</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -639,7 +643,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>p = 19 cm. Compute T = t/N and cos θ, plot T² against cos θ; gradient = εp.</t>
+          <t>p = 19 cm. Compute T = t/N and cos φ, plot T² against cos φ; gradient = εp.</t>
         </is>
       </c>
     </row>
@@ -663,7 +667,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>θ / °</t>
+          <t>φ / °</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -673,7 +677,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>cos θ</t>
+          <t>cos φ</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -686,113 +690,113 @@
       <c r="A6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>42.52</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>41.55</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>39.83</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>37.56</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>34.39</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>30.31</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>25.11</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>17.84</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -846,7 +850,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>θ / °</t>
+          <t>φ / °</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -856,7 +860,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>cos θ</t>
+          <t>cos φ</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -884,21 +888,21 @@
       <c r="A6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>42.52</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D6" s="7">
-        <f>B6/A6</f>
-        <v/>
-      </c>
-      <c r="E6" s="7">
+      <c r="D6" s="9">
+        <f>ROUND(B6/A6,3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="9">
         <f>COS(RADIANS(C6))</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <f>D6^2</f>
         <v/>
       </c>
@@ -907,7 +911,7 @@
           <t>gradient = εp</t>
         </is>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <f>SLOPE(F6:F13,E6:E13)</f>
         <v/>
       </c>
@@ -921,21 +925,21 @@
       <c r="A7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>41.55</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="7">
-        <f>B7/A7</f>
-        <v/>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="9">
+        <f>ROUND(B7/A7,3)</f>
+        <v/>
+      </c>
+      <c r="E7" s="9">
         <f>COS(RADIANS(C7))</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <f>D7^2</f>
         <v/>
       </c>
@@ -944,7 +948,7 @@
           <t>ε = gradient / 0.19</t>
         </is>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <f>SLOPE(F6:F13,E6:E13)/0.19</f>
         <v/>
       </c>
@@ -958,21 +962,21 @@
       <c r="A8" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>39.83</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D8" s="7">
-        <f>B8/A8</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
+      <c r="D8" s="9">
+        <f>ROUND(B8/A8,3)</f>
+        <v/>
+      </c>
+      <c r="E8" s="9">
         <f>COS(RADIANS(C8))</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="9">
         <f>D8^2</f>
         <v/>
       </c>
@@ -981,7 +985,7 @@
           <t>g = 4π²/ε</t>
         </is>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="9">
         <f>4*PI()^2/(SLOPE(F6:F13,E6:E13)/0.19)</f>
         <v/>
       </c>
@@ -995,21 +999,21 @@
       <c r="A9" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>37.56</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="D9" s="7">
-        <f>B9/A9</f>
-        <v/>
-      </c>
-      <c r="E9" s="7">
+      <c r="D9" s="9">
+        <f>ROUND(B9/A9,3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="9">
         <f>COS(RADIANS(C9))</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="9">
         <f>D9^2</f>
         <v/>
       </c>
@@ -1018,21 +1022,21 @@
       <c r="A10" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>34.39</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="D10" s="7">
-        <f>B10/A10</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
+      <c r="D10" s="9">
+        <f>ROUND(B10/A10,3)</f>
+        <v/>
+      </c>
+      <c r="E10" s="9">
         <f>COS(RADIANS(C10))</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="9">
         <f>D10^2</f>
         <v/>
       </c>
@@ -1041,21 +1045,21 @@
       <c r="A11" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>30.31</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="7">
-        <f>B11/A11</f>
-        <v/>
-      </c>
-      <c r="E11" s="7">
+      <c r="D11" s="9">
+        <f>ROUND(B11/A11,3)</f>
+        <v/>
+      </c>
+      <c r="E11" s="9">
         <f>COS(RADIANS(C11))</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="9">
         <f>D11^2</f>
         <v/>
       </c>
@@ -1064,21 +1068,21 @@
       <c r="A12" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>25.11</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="D12" s="7">
-        <f>B12/A12</f>
-        <v/>
-      </c>
-      <c r="E12" s="7">
+      <c r="D12" s="9">
+        <f>ROUND(B12/A12,3)</f>
+        <v/>
+      </c>
+      <c r="E12" s="9">
         <f>COS(RADIANS(C12))</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="9">
         <f>D12^2</f>
         <v/>
       </c>
@@ -1087,21 +1091,21 @@
       <c r="A13" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>17.84</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="D13" s="7">
-        <f>B13/A13</f>
-        <v/>
-      </c>
-      <c r="E13" s="7">
+      <c r="D13" s="9">
+        <f>ROUND(B13/A13,3)</f>
+        <v/>
+      </c>
+      <c r="E13" s="9">
         <f>COS(RADIANS(C13))</f>
         <v/>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="9">
         <f>D13^2</f>
         <v/>
       </c>
